--- a/testData/LoginTestData.xlsx
+++ b/testData/LoginTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mukesh Ojha\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452C7675-C3AD-4116-8E47-F2ADFDF18FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A452974A-2A14-467A-AA80-6210270831F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>Username</t>
   </si>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
@@ -459,45 +459,20 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
+      <c r="A4" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{52F0D25A-6513-4605-8F0E-D83AFC640840}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{0CDA384B-C2E7-4420-867E-DF2B5860CD9C}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{A1DADC14-C308-4E7B-B5E8-7B986040FDA6}"/>
-    <hyperlink ref="A3" r:id="rId4" xr:uid="{5D03B8F5-6BC9-425E-9358-6814201EA432}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{C5472F1D-35C3-4156-A63B-B2A63FD04861}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{5D03B8F5-6BC9-425E-9358-6814201EA432}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
